--- a/resumo_consolidado_alimentadores.xlsx
+++ b/resumo_consolidado_alimentadores.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,7 +671,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Base 60%</t>
+          <t>Rede 20%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
@@ -693,28 +693,28 @@
         <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>2961.48</v>
+        <v>987.1599999999996</v>
       </c>
       <c r="J2" t="n">
-        <v>3219</v>
+        <v>1073</v>
       </c>
       <c r="K2" t="n">
-        <v>2886.58042635486</v>
+        <v>994.704334291993</v>
       </c>
       <c r="L2" t="n">
-        <v>1339.075442532227</v>
+        <v>433.9601259452516</v>
       </c>
       <c r="M2" t="n">
-        <v>3182.054304786121</v>
+        <v>1085.245642041329</v>
       </c>
       <c r="N2" t="n">
-        <v>133.2607904603353</v>
+        <v>45.41838397754081</v>
       </c>
       <c r="O2" t="n">
-        <v>133.2609726624506</v>
+        <v>45.41844437719622</v>
       </c>
       <c r="P2" t="n">
-        <v>133.261</v>
+        <v>45.4189</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>0.999</v>
+        <v>0.9996699999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>2634.181909253616</v>
+        <v>987.1461730154401</v>
       </c>
       <c r="T2" t="n">
-        <v>1122.15658848309</v>
+        <v>420.523167460133</v>
       </c>
       <c r="U2" t="n">
-        <v>2863.241125039076</v>
+        <v>1072.985228821782</v>
       </c>
       <c r="V2" t="n">
-        <v>88.94815799038372</v>
+        <v>99.99859931677139</v>
       </c>
       <c r="W2" t="n">
-        <v>252.3985171012438</v>
+        <v>7.55816127655278</v>
       </c>
       <c r="X2" t="n">
-        <v>216.9188540491372</v>
+        <v>13.43695848511854</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9061900000000001</v>
+        <v>0.99378</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9263401335877863</v>
+        <v>0.9951274045801527</v>
       </c>
       <c r="AA2" t="n">
-        <v>133.261</v>
+        <v>45.4189</v>
       </c>
       <c r="AB2" t="n">
-        <v>92.14660679430739</v>
+        <v>99.24017057586912</v>
       </c>
       <c r="AC2" t="n">
-        <v>91.2561411836368</v>
+        <v>99.24016001378615</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
@@ -783,19 +783,19 @@
         <v>0.92</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO2" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rede 80%</t>
+          <t>Rede 40%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
@@ -860,28 +860,28 @@
         <v>54</v>
       </c>
       <c r="I3" t="n">
-        <v>3948.639999999999</v>
+        <v>1974.319999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4292</v>
+        <v>2146</v>
       </c>
       <c r="K3" t="n">
-        <v>3693.458314408895</v>
+        <v>2005.10415052042</v>
       </c>
       <c r="L3" t="n">
-        <v>1754.038779670179</v>
+        <v>896.0179024154437</v>
       </c>
       <c r="M3" t="n">
-        <v>4088.800112607982</v>
+        <v>2196.199156698497</v>
       </c>
       <c r="N3" t="n">
-        <v>171.2857037102429</v>
+        <v>91.94485397272364</v>
       </c>
       <c r="O3" t="n">
-        <v>171.2859907845542</v>
+        <v>91.94472710639172</v>
       </c>
       <c r="P3" t="n">
-        <v>171.286</v>
+        <v>91.94540000000001</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -889,40 +889,40 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>0.9987</v>
+        <v>0.99932</v>
       </c>
       <c r="S3" t="n">
-        <v>3277.365568592422</v>
+        <v>1974.12516803001</v>
       </c>
       <c r="T3" t="n">
-        <v>1396.15963830713</v>
+        <v>840.9641283674644</v>
       </c>
       <c r="U3" t="n">
-        <v>3562.356917243558</v>
+        <v>2145.78443564361</v>
       </c>
       <c r="V3" t="n">
-        <v>82.99985738361622</v>
+        <v>99.99013169243138</v>
       </c>
       <c r="W3" t="n">
-        <v>416.0927458164726</v>
+        <v>30.97898249040999</v>
       </c>
       <c r="X3" t="n">
-        <v>357.8791413630492</v>
+        <v>55.05377404797935</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.87949</v>
+        <v>0.98738</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9053285050890585</v>
+        <v>0.9901064821882953</v>
       </c>
       <c r="AA3" t="n">
-        <v>171.286</v>
+        <v>91.94540000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>90.46693646443093</v>
+        <v>98.45514395803777</v>
       </c>
       <c r="AC3" t="n">
-        <v>88.73433215170687</v>
+        <v>98.45499384745828</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
@@ -950,19 +950,19 @@
         <v>0.92</v>
       </c>
       <c r="AK3" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO3" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rede 100%</t>
+          <t>Base 60%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1017,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
@@ -1027,28 +1027,28 @@
         <v>54</v>
       </c>
       <c r="I4" t="n">
-        <v>4935.800000000001</v>
+        <v>2961.48</v>
       </c>
       <c r="J4" t="n">
-        <v>5365</v>
+        <v>3219</v>
       </c>
       <c r="K4" t="n">
-        <v>4437.144701715955</v>
+        <v>3032.946244030377</v>
       </c>
       <c r="L4" t="n">
-        <v>2153.025403019555</v>
+        <v>1388.649705686515</v>
       </c>
       <c r="M4" t="n">
-        <v>4931.913572845076</v>
+        <v>3335.732441950525</v>
       </c>
       <c r="N4" t="n">
-        <v>206.6649471864666</v>
+        <v>139.7022485489767</v>
       </c>
       <c r="O4" t="n">
-        <v>206.6642770682244</v>
+        <v>139.7027143652236</v>
       </c>
       <c r="P4" t="n">
-        <v>206.665</v>
+        <v>139.703</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1056,40 +1056,40 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>0.9984100000000001</v>
+        <v>0.99896</v>
       </c>
       <c r="S4" t="n">
-        <v>3832.686585156781</v>
+        <v>2961.416149559498</v>
       </c>
       <c r="T4" t="n">
-        <v>1632.726080397145</v>
+        <v>1261.549564814277</v>
       </c>
       <c r="U4" t="n">
-        <v>4165.966984224644</v>
+        <v>3218.92729264811</v>
       </c>
       <c r="V4" t="n">
-        <v>77.65076755858787</v>
+        <v>99.99784396853931</v>
       </c>
       <c r="W4" t="n">
-        <v>604.4581165591743</v>
+        <v>71.53009447087857</v>
       </c>
       <c r="X4" t="n">
-        <v>520.2993226224098</v>
+        <v>127.1001408722385</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8546999999999999</v>
+        <v>0.9807799999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8857931933842238</v>
+        <v>0.9849217811704835</v>
       </c>
       <c r="AA4" t="n">
-        <v>206.665</v>
+        <v>139.703</v>
       </c>
       <c r="AB4" t="n">
-        <v>89.08971199820961</v>
+        <v>97.64161370246421</v>
       </c>
       <c r="AC4" t="n">
-        <v>86.37731791065062</v>
+        <v>97.64156405305012</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -1117,19 +1117,19 @@
         <v>0.92</v>
       </c>
       <c r="AK4" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO4" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rede 120%</t>
+          <t>Rede 80%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
@@ -1194,28 +1194,28 @@
         <v>54</v>
       </c>
       <c r="I5" t="n">
-        <v>5922.96</v>
+        <v>3948.639999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>6438</v>
+        <v>4292</v>
       </c>
       <c r="K5" t="n">
-        <v>5124.533320616601</v>
+        <v>4074.138133150899</v>
       </c>
       <c r="L5" t="n">
-        <v>2536.297134911286</v>
+        <v>1911.583396840596</v>
       </c>
       <c r="M5" t="n">
-        <v>5717.835684126381</v>
+        <v>4500.305835281744</v>
       </c>
       <c r="N5" t="n">
-        <v>239.6627271226231</v>
+        <v>188.5469239824579</v>
       </c>
       <c r="O5" t="n">
-        <v>239.6621395654671</v>
+        <v>188.547843501066</v>
       </c>
       <c r="P5" t="n">
-        <v>239.662</v>
+        <v>188.548</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1223,40 +1223,40 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.9981399999999999</v>
+        <v>0.99858</v>
       </c>
       <c r="S5" t="n">
-        <v>4313.297983387087</v>
+        <v>3943.849270324201</v>
       </c>
       <c r="T5" t="n">
-        <v>1837.457694065066</v>
+        <v>1680.070783793404</v>
       </c>
       <c r="U5" t="n">
-        <v>4688.367548621804</v>
+        <v>4286.79191302691</v>
       </c>
       <c r="V5" t="n">
-        <v>72.82335155711142</v>
+        <v>99.87867393138403</v>
       </c>
       <c r="W5" t="n">
-        <v>811.2353372295142</v>
+        <v>130.2888628266981</v>
       </c>
       <c r="X5" t="n">
-        <v>698.8394408462195</v>
+        <v>231.512613047192</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.83162</v>
+        <v>0.9739999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8675907824427481</v>
+        <v>0.9795912468193385</v>
       </c>
       <c r="AA5" t="n">
-        <v>239.662</v>
+        <v>188.548</v>
       </c>
       <c r="AB5" t="n">
-        <v>87.95349263564337</v>
+        <v>96.80580693588247</v>
       </c>
       <c r="AC5" t="n">
-        <v>84.16957630140058</v>
+        <v>96.80205092295351</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1284,19 +1284,19 @@
         <v>0.92</v>
       </c>
       <c r="AK5" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO5" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rede 160%</t>
+          <t>Rede 100%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
@@ -1361,28 +1361,28 @@
         <v>54</v>
       </c>
       <c r="I6" t="n">
-        <v>7897.279999999997</v>
+        <v>4935.800000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>8584</v>
+        <v>5365</v>
       </c>
       <c r="K6" t="n">
-        <v>6353.467713561111</v>
+        <v>5020.082839082584</v>
       </c>
       <c r="L6" t="n">
-        <v>3257.503031282816</v>
+        <v>2408.062051635827</v>
       </c>
       <c r="M6" t="n">
-        <v>7139.879409771582</v>
+        <v>5567.763873924612</v>
       </c>
       <c r="N6" t="n">
-        <v>299.4175892216566</v>
+        <v>233.3537734409748</v>
       </c>
       <c r="O6" t="n">
-        <v>299.4175228622893</v>
+        <v>233.3543189068799</v>
       </c>
       <c r="P6" t="n">
-        <v>299.418</v>
+        <v>233.355</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -1390,40 +1390,40 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0.99764</v>
+        <v>0.99822</v>
       </c>
       <c r="S6" t="n">
-        <v>5092.236173954713</v>
+        <v>4820.740684876349</v>
       </c>
       <c r="T6" t="n">
-        <v>2169.28134558771</v>
+        <v>2053.617363856509</v>
       </c>
       <c r="U6" t="n">
-        <v>5535.038464875178</v>
+        <v>5239.931777032507</v>
       </c>
       <c r="V6" t="n">
-        <v>64.48088676043797</v>
+        <v>97.66888214425926</v>
       </c>
       <c r="W6" t="n">
-        <v>1261.231539606398</v>
+        <v>199.3421542062339</v>
       </c>
       <c r="X6" t="n">
-        <v>1088.221685695106</v>
+        <v>354.4446877793184</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.78999</v>
+        <v>0.9678</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8346914185750636</v>
+        <v>0.9746926526717559</v>
       </c>
       <c r="AA6" t="n">
-        <v>299.418</v>
+        <v>233.355</v>
       </c>
       <c r="AB6" t="n">
-        <v>86.228858978316</v>
+        <v>96.11807914522967</v>
       </c>
       <c r="AC6" t="n">
-        <v>80.14892659461586</v>
+        <v>96.0291062797947</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
@@ -1451,19 +1451,19 @@
         <v>0.92</v>
       </c>
       <c r="AK6" t="n">
-        <v>512</v>
+        <v>86</v>
       </c>
       <c r="AL6" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO6" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trafo alvo 50%</t>
+          <t>Rede 120%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1518,11 +1518,9 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>0.92</v>
       </c>
@@ -1530,28 +1528,28 @@
         <v>54</v>
       </c>
       <c r="I7" t="n">
-        <v>2933.88</v>
+        <v>5922.96</v>
       </c>
       <c r="J7" t="n">
-        <v>3189</v>
+        <v>6438</v>
       </c>
       <c r="K7" t="n">
-        <v>2860.605677514181</v>
+        <v>5917.355457406423</v>
       </c>
       <c r="L7" t="n">
-        <v>1326.396716954178</v>
+        <v>2898.590546295986</v>
       </c>
       <c r="M7" t="n">
-        <v>3153.156052746706</v>
+        <v>6589.151900235267</v>
       </c>
       <c r="N7" t="n">
-        <v>132.0492429425573</v>
+        <v>276.2586209591768</v>
       </c>
       <c r="O7" t="n">
-        <v>132.0495117512078</v>
+        <v>276.2589889734937</v>
       </c>
       <c r="P7" t="n">
-        <v>132.05</v>
+        <v>276.259</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1559,40 +1557,40 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>0.9990099999999998</v>
+        <v>0.9978700000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>2610.781188007151</v>
+        <v>5638.01217305752</v>
       </c>
       <c r="T7" t="n">
-        <v>1112.193530859321</v>
+        <v>2401.856430549627</v>
       </c>
       <c r="U7" t="n">
-        <v>2837.807756303685</v>
+        <v>6128.302830027035</v>
       </c>
       <c r="V7" t="n">
-        <v>88.9873201360366</v>
+        <v>95.18909756367627</v>
       </c>
       <c r="W7" t="n">
-        <v>249.8244895070302</v>
+        <v>279.3432843489025</v>
       </c>
       <c r="X7" t="n">
-        <v>214.2031860948571</v>
+        <v>496.7341157463594</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.90657</v>
+        <v>0.96182</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9267225190839695</v>
+        <v>0.9699693129770992</v>
       </c>
       <c r="AA7" t="n">
-        <v>132.05</v>
+        <v>276.259</v>
       </c>
       <c r="AB7" t="n">
-        <v>92.15302518401407</v>
+        <v>95.49613632964697</v>
       </c>
       <c r="AC7" t="n">
-        <v>91.26672748114925</v>
+        <v>95.27925462041891</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1620,19 +1618,19 @@
         <v>0.92</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AL7" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO7" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -1675,7 +1673,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trafo alvo 80%</t>
+          <t>Trafo alvo 50%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1690,7 +1688,7 @@
         <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
         <v>0.92</v>
@@ -1699,28 +1697,28 @@
         <v>54</v>
       </c>
       <c r="I8" t="n">
-        <v>3016.68</v>
+        <v>2933.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3279</v>
+        <v>3189</v>
       </c>
       <c r="K8" t="n">
-        <v>2937.569957417619</v>
+        <v>3004.293284450475</v>
       </c>
       <c r="L8" t="n">
-        <v>1364.706835818605</v>
+        <v>1374.836731827019</v>
       </c>
       <c r="M8" t="n">
-        <v>3239.095861880685</v>
+        <v>3303.930110970119</v>
       </c>
       <c r="N8" t="n">
-        <v>135.6523413147945</v>
+        <v>138.3689648854485</v>
       </c>
       <c r="O8" t="n">
-        <v>135.652347716438</v>
+        <v>138.3693968814632</v>
       </c>
       <c r="P8" t="n">
-        <v>135.653</v>
+        <v>138.37</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1728,40 +1726,40 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>0.99898</v>
+        <v>0.99897</v>
       </c>
       <c r="S8" t="n">
-        <v>2679.773193990217</v>
+        <v>2933.817962749476</v>
       </c>
       <c r="T8" t="n">
-        <v>1141.57658460559</v>
+        <v>1249.794758104195</v>
       </c>
       <c r="U8" t="n">
-        <v>2912.796160006446</v>
+        <v>3188.930036224722</v>
       </c>
       <c r="V8" t="n">
-        <v>88.83186794722069</v>
+        <v>99.9978854878003</v>
       </c>
       <c r="W8" t="n">
-        <v>257.7967634274015</v>
+        <v>70.47532170099913</v>
       </c>
       <c r="X8" t="n">
-        <v>223.1302512130153</v>
+        <v>125.0419737228241</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.90542</v>
+        <v>0.98089</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9255834287531807</v>
+        <v>0.9850307569974555</v>
       </c>
       <c r="AA8" t="n">
-        <v>135.653</v>
+        <v>138.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>92.12708527033293</v>
+        <v>97.6542281403287</v>
       </c>
       <c r="AC8" t="n">
-        <v>91.22414896787591</v>
+        <v>97.65417970123747</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1789,19 +1787,19 @@
         <v>0.92</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO8" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1844,7 +1842,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trafo alvo 100%</t>
+          <t>Trafo alvo 80%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1859,7 +1857,7 @@
         <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
         <v>0.92</v>
@@ -1868,28 +1866,28 @@
         <v>54</v>
       </c>
       <c r="I9" t="n">
-        <v>3071.88</v>
+        <v>3016.68</v>
       </c>
       <c r="J9" t="n">
-        <v>3339</v>
+        <v>3279</v>
       </c>
       <c r="K9" t="n">
-        <v>2987.306236212956</v>
+        <v>3090.572647890959</v>
       </c>
       <c r="L9" t="n">
-        <v>1390.661116160967</v>
+        <v>1417.243879113477</v>
       </c>
       <c r="M9" t="n">
-        <v>3295.138371740842</v>
+        <v>3400.032279960934</v>
       </c>
       <c r="N9" t="n">
-        <v>138.0021473014283</v>
+        <v>142.3980108834831</v>
       </c>
       <c r="O9" t="n">
-        <v>138.0019723234304</v>
+        <v>142.3986189556756</v>
       </c>
       <c r="P9" t="n">
-        <v>138.003</v>
+        <v>142.399</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1897,40 +1895,40 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0.99896</v>
+        <v>0.9989400000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>2723.795368109696</v>
+        <v>3016.608537990603</v>
       </c>
       <c r="T9" t="n">
-        <v>1160.327099098108</v>
+        <v>1285.058366240926</v>
       </c>
       <c r="U9" t="n">
-        <v>2960.645231066577</v>
+        <v>3278.917820885971</v>
       </c>
       <c r="V9" t="n">
-        <v>88.66867742586611</v>
+        <v>99.99763110408139</v>
       </c>
       <c r="W9" t="n">
-        <v>263.5108681032603</v>
+        <v>73.96410990035621</v>
       </c>
       <c r="X9" t="n">
-        <v>230.3340170628588</v>
+        <v>132.1855128725507</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.90467</v>
+        <v>0.98055</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9248393384223919</v>
+        <v>0.9847019402035622</v>
       </c>
       <c r="AA9" t="n">
-        <v>138.003</v>
+        <v>142.399</v>
       </c>
       <c r="AB9" t="n">
-        <v>92.09955059170888</v>
+        <v>97.60683833950907</v>
       </c>
       <c r="AC9" t="n">
-        <v>91.17898041690843</v>
+        <v>97.60678300344014</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -1958,19 +1956,19 @@
         <v>0.92</v>
       </c>
       <c r="AK9" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO9" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -2013,7 +2011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trafo alvo 120%</t>
+          <t>Trafo alvo 100%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2028,7 +2026,7 @@
         <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
         <v>0.92</v>
@@ -2037,28 +2035,28 @@
         <v>54</v>
       </c>
       <c r="I10" t="n">
-        <v>3127.08</v>
+        <v>3071.88</v>
       </c>
       <c r="J10" t="n">
-        <v>3399</v>
+        <v>3339</v>
       </c>
       <c r="K10" t="n">
-        <v>3035.806111365074</v>
+        <v>3148.653652253272</v>
       </c>
       <c r="L10" t="n">
-        <v>1416.905540660937</v>
+        <v>1447.17891250351</v>
       </c>
       <c r="M10" t="n">
-        <v>3350.185078015421</v>
+        <v>3465.30613750686</v>
       </c>
       <c r="N10" t="n">
-        <v>140.3103417613446</v>
+        <v>145.1361281850875</v>
       </c>
       <c r="O10" t="n">
-        <v>140.3099780737957</v>
+        <v>145.1355338075397</v>
       </c>
       <c r="P10" t="n">
-        <v>140.31</v>
+        <v>145.136</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -2066,40 +2064,40 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>0.9989400000000001</v>
+        <v>0.99891</v>
       </c>
       <c r="S10" t="n">
-        <v>2766.286998626746</v>
+        <v>3071.80592704831</v>
       </c>
       <c r="T10" t="n">
-        <v>1178.43139450332</v>
+        <v>1308.565819647354</v>
       </c>
       <c r="U10" t="n">
-        <v>3006.832936882662</v>
+        <v>3338.912421402885</v>
       </c>
       <c r="V10" t="n">
-        <v>88.46230344688163</v>
+        <v>99.99758867691152</v>
       </c>
       <c r="W10" t="n">
-        <v>269.5191127383278</v>
+        <v>76.84772520496198</v>
       </c>
       <c r="X10" t="n">
-        <v>238.4741461576171</v>
+        <v>138.6130928561566</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.90393</v>
+        <v>0.98032</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9241063931297711</v>
+        <v>0.9844772010178119</v>
       </c>
       <c r="AA10" t="n">
-        <v>140.31</v>
+        <v>145.136</v>
       </c>
       <c r="AB10" t="n">
-        <v>92.06503023192978</v>
+        <v>97.55940392718587</v>
       </c>
       <c r="AC10" t="n">
-        <v>91.12199189107184</v>
+        <v>97.55934651148539</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2127,19 +2125,19 @@
         <v>0.92</v>
       </c>
       <c r="AK10" t="n">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO10" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2182,7 +2180,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trafo alvo 150%</t>
+          <t>Trafo alvo 120%</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2197,7 +2195,7 @@
         <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G11" t="n">
         <v>0.92</v>
@@ -2206,28 +2204,28 @@
         <v>54</v>
       </c>
       <c r="I11" t="n">
-        <v>3209.88</v>
+        <v>3127.08</v>
       </c>
       <c r="J11" t="n">
-        <v>3489</v>
+        <v>3399</v>
       </c>
       <c r="K11" t="n">
-        <v>3106.29239668546</v>
+        <v>3205.691721499833</v>
       </c>
       <c r="L11" t="n">
-        <v>1456.728576477176</v>
+        <v>1477.718162260582</v>
       </c>
       <c r="M11" t="n">
-        <v>3430.905215716563</v>
+        <v>3529.888154087514</v>
       </c>
       <c r="N11" t="n">
-        <v>143.6953271716932</v>
+        <v>147.8439528725942</v>
       </c>
       <c r="O11" t="n">
-        <v>143.694661723036</v>
+        <v>147.8436154606583</v>
       </c>
       <c r="P11" t="n">
-        <v>143.695</v>
+        <v>147.844</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2235,40 +2233,40 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0.99891</v>
+        <v>0.9988899999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>2827.250777592329</v>
+        <v>3125.580605061593</v>
       </c>
       <c r="T11" t="n">
-        <v>1204.403487847856</v>
+        <v>1331.48761341777</v>
       </c>
       <c r="U11" t="n">
-        <v>3073.098553729852</v>
+        <v>3397.368596932358</v>
       </c>
       <c r="V11" t="n">
-        <v>88.07964090845542</v>
+        <v>99.95205127664123</v>
       </c>
       <c r="W11" t="n">
-        <v>279.0416190931304</v>
+        <v>80.11111643823985</v>
       </c>
       <c r="X11" t="n">
-        <v>252.3250886293196</v>
+        <v>146.2305488428124</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.90284</v>
+        <v>0.98009</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.9230302353689568</v>
+        <v>0.9842538422391858</v>
       </c>
       <c r="AA11" t="n">
-        <v>143.695</v>
+        <v>147.844</v>
       </c>
       <c r="AB11" t="n">
-        <v>92.00206684019284</v>
+        <v>97.50214086003058</v>
       </c>
       <c r="AC11" t="n">
-        <v>91.01689141077384</v>
+        <v>97.50097253890779</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2296,19 +2294,19 @@
         <v>0.92</v>
       </c>
       <c r="AK11" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="AO11" t="n">
-        <v>448</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -2340,6 +2338,175 @@
         </is>
       </c>
       <c r="AW11" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ES11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trafo alvo 150%</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Snapshot estático</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>150</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3209.88</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3489</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3284.267791099011</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1521.629851751886</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3619.637043875096</v>
+      </c>
+      <c r="N12" t="n">
+        <v>151.6075007864058</v>
+      </c>
+      <c r="O12" t="n">
+        <v>151.6072980996564</v>
+      </c>
+      <c r="P12" t="n">
+        <v>151.608</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>LINE.L_TR_FIC_GER_41</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.99886</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3198.942807066718</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1362.732202073194</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3477.107150700298</v>
+      </c>
+      <c r="V12" t="n">
+        <v>99.65926474094726</v>
+      </c>
+      <c r="W12" t="n">
+        <v>85.32498403229282</v>
+      </c>
+      <c r="X12" t="n">
+        <v>158.8976496786923</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.9797699999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.9839407760814247</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>151.608</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>97.41063198053671</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>97.40200892681347</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>wye</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>448</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>ES_ALES11</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>CTMT coluna 'PAC_INI'</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>SES_ES11_9154_BSB118</t>
+        </is>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.215143057611051</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>525</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>525</v>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>FP7255</t>
+        </is>
+      </c>
+      <c r="AW12" t="n">
         <v>300</v>
       </c>
     </row>
